--- a/Allas tips excel/Anna_N_VM_Tips_2026 Anna.xlsx
+++ b/Allas tips excel/Anna_N_VM_Tips_2026 Anna.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VM2026\Allas tips excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9875FFD8-C51D-461B-8AB5-64657CC760E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD36A83A-3323-441A-8B9A-E8F616A73EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27090" yWindow="270" windowWidth="25455" windowHeight="15135" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25455" windowHeight="15135" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instruktion" sheetId="1" r:id="rId1"/>
@@ -3794,7 +3794,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4285,6 +4285,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4294,8 +4302,6 @@
     <xf numFmtId="0" fontId="2" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="56" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4320,8 +4326,14 @@
     <xf numFmtId="0" fontId="11" fillId="29" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="57" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4341,9 +4353,6 @@
     <xf numFmtId="0" fontId="16" fillId="57" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="58" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4352,9 +4361,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="58" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4369,13 +4375,6 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4978,10 +4977,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="194" t="s">
         <v>919</v>
       </c>
-      <c r="B1" s="191"/>
+      <c r="B1" s="195"/>
       <c r="C1" s="111"/>
       <c r="D1" s="111"/>
       <c r="E1" s="111"/>
@@ -5074,48 +5073,48 @@
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="32" width="15" customWidth="1"/>
-    <col min="33" max="33" width="15" style="222" customWidth="1"/>
+    <col min="33" max="33" width="15" style="111" customWidth="1"/>
     <col min="34" max="35" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A1" s="220" t="s">
+      <c r="A1" s="190" t="s">
         <v>875</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
-      <c r="V1" s="193"/>
-      <c r="W1" s="193"/>
-      <c r="X1" s="193"/>
-      <c r="Y1" s="193"/>
-      <c r="Z1" s="193"/>
-      <c r="AA1" s="193"/>
-      <c r="AB1" s="193"/>
-      <c r="AC1" s="193"/>
-      <c r="AD1" s="193"/>
-      <c r="AE1" s="193"/>
-      <c r="AF1" s="193"/>
-      <c r="AG1" s="193"/>
-      <c r="AH1" s="193"/>
-      <c r="AI1" s="194"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="191"/>
+      <c r="G1" s="191"/>
+      <c r="H1" s="191"/>
+      <c r="I1" s="191"/>
+      <c r="J1" s="191"/>
+      <c r="K1" s="191"/>
+      <c r="L1" s="191"/>
+      <c r="M1" s="191"/>
+      <c r="N1" s="191"/>
+      <c r="O1" s="191"/>
+      <c r="P1" s="191"/>
+      <c r="Q1" s="191"/>
+      <c r="R1" s="191"/>
+      <c r="S1" s="191"/>
+      <c r="T1" s="191"/>
+      <c r="U1" s="191"/>
+      <c r="V1" s="191"/>
+      <c r="W1" s="191"/>
+      <c r="X1" s="191"/>
+      <c r="Y1" s="191"/>
+      <c r="Z1" s="191"/>
+      <c r="AA1" s="191"/>
+      <c r="AB1" s="191"/>
+      <c r="AC1" s="191"/>
+      <c r="AD1" s="191"/>
+      <c r="AE1" s="191"/>
+      <c r="AF1" s="191"/>
+      <c r="AG1" s="191"/>
+      <c r="AH1" s="191"/>
+      <c r="AI1" s="192"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -5362,17 +5361,16 @@
         <v>Lamine Yamal</v>
       </c>
       <c r="AI3" s="2">
-        <f>'4. Skyttekung och utslagsfråga'!C6</f>
-        <v>6</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A6" s="221" t="s">
+      <c r="A6" s="193" t="s">
         <v>909</v>
       </c>
-      <c r="B6" s="193"/>
-      <c r="C6" s="193"/>
-      <c r="D6" s="194"/>
+      <c r="B6" s="191"/>
+      <c r="C6" s="191"/>
+      <c r="D6" s="192"/>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -5622,29 +5620,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="196" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="194"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="192"/>
       <c r="G1" s="85"/>
       <c r="H1" s="34"/>
       <c r="I1" s="34"/>
       <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="201" t="s">
+      <c r="A2" s="203" t="s">
         <v>929</v>
       </c>
-      <c r="B2" s="201"/>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
-      <c r="G2" s="201"/>
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
       <c r="H2" s="54"/>
       <c r="I2" s="54"/>
     </row>
@@ -6414,20 +6412,20 @@
       <c r="G58" s="112"/>
     </row>
     <row r="59" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="198" t="s">
+      <c r="B59" s="200" t="s">
         <v>922</v>
       </c>
-      <c r="C59" s="199"/>
-      <c r="D59" s="199"/>
-      <c r="E59" s="200"/>
+      <c r="C59" s="201"/>
+      <c r="D59" s="201"/>
+      <c r="E59" s="202"/>
     </row>
     <row r="60" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="195" t="s">
+      <c r="A60" s="197" t="s">
         <v>312</v>
       </c>
-      <c r="B60" s="196"/>
-      <c r="C60" s="196"/>
-      <c r="D60" s="197"/>
+      <c r="B60" s="198"/>
+      <c r="C60" s="198"/>
+      <c r="D60" s="199"/>
     </row>
     <row r="61" spans="1:7" s="111" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="91" t="s">
@@ -6872,24 +6870,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="196" t="s">
         <v>918</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="194"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="192"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="202" t="s">
+      <c r="A2" s="204" t="s">
         <v>923</v>
       </c>
-      <c r="B2" s="202"/>
-      <c r="C2" s="202"/>
-      <c r="D2" s="202"/>
-      <c r="E2" s="202"/>
-      <c r="F2" s="202"/>
+      <c r="B2" s="204"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
     </row>
     <row r="3" spans="1:6" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6987,11 +6985,11 @@
     </row>
     <row r="19" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="198" t="s">
+      <c r="B20" s="200" t="s">
         <v>922</v>
       </c>
-      <c r="C20" s="199"/>
-      <c r="D20" s="200"/>
+      <c r="C20" s="201"/>
+      <c r="D20" s="202"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G27" s="177"/>
@@ -7159,32 +7157,32 @@
     </row>
     <row r="3" spans="2:35" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="127"/>
-      <c r="O3" s="204" t="s">
+      <c r="O3" s="208" t="s">
         <v>353</v>
       </c>
-      <c r="P3" s="205"/>
-      <c r="Q3" s="205"/>
-      <c r="R3" s="205"/>
-      <c r="S3" s="206"/>
+      <c r="P3" s="209"/>
+      <c r="Q3" s="209"/>
+      <c r="R3" s="209"/>
+      <c r="S3" s="210"/>
       <c r="AF3" s="128"/>
     </row>
     <row r="4" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="127"/>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="205" t="s">
         <v>914</v>
       </c>
-      <c r="D4" s="210"/>
-      <c r="E4" s="210"/>
-      <c r="O4" s="207"/>
-      <c r="P4" s="208"/>
-      <c r="Q4" s="208"/>
-      <c r="R4" s="208"/>
-      <c r="S4" s="209"/>
-      <c r="AC4" s="210" t="s">
+      <c r="D4" s="205"/>
+      <c r="E4" s="205"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="212"/>
+      <c r="Q4" s="212"/>
+      <c r="R4" s="212"/>
+      <c r="S4" s="213"/>
+      <c r="AC4" s="205" t="s">
         <v>914</v>
       </c>
-      <c r="AD4" s="210"/>
-      <c r="AE4" s="210"/>
+      <c r="AD4" s="205"/>
+      <c r="AE4" s="205"/>
       <c r="AF4" s="128"/>
     </row>
     <row r="5" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7225,7 +7223,7 @@
     </row>
     <row r="6" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="127"/>
-      <c r="C6" s="214" t="s">
+      <c r="C6" s="207" t="s">
         <v>251</v>
       </c>
       <c r="D6" s="115" t="str">
@@ -7259,7 +7257,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M76",_Listor!$BX$3:$BX$18,0),1)</f>
         <v>Brasilien</v>
       </c>
-      <c r="AE6" s="203" t="s">
+      <c r="AE6" s="206" t="s">
         <v>253</v>
       </c>
       <c r="AF6" s="128"/>
@@ -7269,13 +7267,13 @@
     </row>
     <row r="7" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="127"/>
-      <c r="C7" s="214"/>
+      <c r="C7" s="207"/>
       <c r="E7" s="114"/>
-      <c r="F7" s="210" t="s">
+      <c r="F7" s="205" t="s">
         <v>913</v>
       </c>
-      <c r="G7" s="210"/>
-      <c r="H7" s="210"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="205"/>
       <c r="I7" s="114"/>
       <c r="J7" s="114"/>
       <c r="K7" s="114"/>
@@ -7293,13 +7291,13 @@
       <c r="W7" s="114"/>
       <c r="X7" s="114"/>
       <c r="Y7" s="114"/>
-      <c r="Z7" s="210" t="s">
+      <c r="Z7" s="205" t="s">
         <v>913</v>
       </c>
-      <c r="AA7" s="210"/>
-      <c r="AB7" s="210"/>
+      <c r="AA7" s="205"/>
+      <c r="AB7" s="205"/>
       <c r="AC7" s="114"/>
-      <c r="AE7" s="203"/>
+      <c r="AE7" s="206"/>
       <c r="AF7" s="128"/>
       <c r="AG7" s="119"/>
       <c r="AH7" s="114"/>
@@ -7307,7 +7305,7 @@
     </row>
     <row r="8" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="127"/>
-      <c r="C8" s="214"/>
+      <c r="C8" s="207"/>
       <c r="D8" s="122" t="str">
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M74",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>USA</v>
@@ -7341,7 +7339,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M76",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Japan</v>
       </c>
-      <c r="AE8" s="203"/>
+      <c r="AE8" s="206"/>
       <c r="AF8" s="128"/>
       <c r="AG8" s="119"/>
       <c r="AH8" s="114"/>
@@ -7352,7 +7350,7 @@
       <c r="C9" s="123"/>
       <c r="D9" s="114"/>
       <c r="E9" s="114"/>
-      <c r="F9" s="203" t="s">
+      <c r="F9" s="206" t="s">
         <v>265</v>
       </c>
       <c r="G9" s="115" t="s">
@@ -7374,7 +7372,7 @@
       <c r="AA9" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="AB9" s="203" t="s">
+      <c r="AB9" s="206" t="s">
         <v>267</v>
       </c>
       <c r="AD9" s="114"/>
@@ -7389,7 +7387,7 @@
       <c r="C10" s="123"/>
       <c r="D10" s="114"/>
       <c r="E10" s="114"/>
-      <c r="F10" s="203"/>
+      <c r="F10" s="206"/>
       <c r="G10" s="114"/>
       <c r="H10" s="114"/>
       <c r="I10" s="114"/>
@@ -7408,7 +7406,7 @@
       <c r="W10" s="120"/>
       <c r="Z10" s="114"/>
       <c r="AA10" s="114"/>
-      <c r="AB10" s="203"/>
+      <c r="AB10" s="206"/>
       <c r="AD10" s="114"/>
       <c r="AE10" s="114"/>
       <c r="AF10" s="130"/>
@@ -7421,7 +7419,7 @@
       <c r="C11" s="123"/>
       <c r="D11" s="114"/>
       <c r="E11" s="114"/>
-      <c r="F11" s="203"/>
+      <c r="F11" s="206"/>
       <c r="G11" s="115" t="s">
         <v>95</v>
       </c>
@@ -7447,7 +7445,7 @@
       <c r="AA11" s="115" t="s">
         <v>97</v>
       </c>
-      <c r="AB11" s="203"/>
+      <c r="AB11" s="206"/>
       <c r="AD11" s="114"/>
       <c r="AE11" s="114"/>
       <c r="AF11" s="130"/>
@@ -7457,7 +7455,7 @@
     </row>
     <row r="12" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="127"/>
-      <c r="C12" s="203" t="s">
+      <c r="C12" s="206" t="s">
         <v>252</v>
       </c>
       <c r="D12" s="115" t="str">
@@ -7486,7 +7484,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M78",_Listor!$BX$3:$BX$18,0),1)</f>
         <v>Elfenbenskusten</v>
       </c>
-      <c r="AE12" s="203" t="s">
+      <c r="AE12" s="206" t="s">
         <v>254</v>
       </c>
       <c r="AF12" s="128"/>
@@ -7496,33 +7494,33 @@
     </row>
     <row r="13" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="127"/>
-      <c r="C13" s="203"/>
+      <c r="C13" s="206"/>
       <c r="D13" s="114"/>
       <c r="E13" s="114"/>
       <c r="F13" s="114"/>
       <c r="G13" s="114"/>
       <c r="H13" s="114"/>
-      <c r="I13" s="210" t="s">
+      <c r="I13" s="205" t="s">
         <v>915</v>
       </c>
-      <c r="J13" s="210"/>
-      <c r="K13" s="210"/>
+      <c r="J13" s="205"/>
+      <c r="K13" s="205"/>
       <c r="L13" s="114"/>
       <c r="M13" s="114"/>
       <c r="N13" s="114"/>
       <c r="T13" s="114"/>
       <c r="U13" s="114"/>
       <c r="V13" s="114"/>
-      <c r="W13" s="210" t="s">
+      <c r="W13" s="205" t="s">
         <v>915</v>
       </c>
-      <c r="X13" s="210"/>
-      <c r="Y13" s="210"/>
+      <c r="X13" s="205"/>
+      <c r="Y13" s="205"/>
       <c r="Z13" s="114"/>
       <c r="AA13" s="114"/>
       <c r="AB13" s="114"/>
       <c r="AC13" s="114"/>
-      <c r="AE13" s="203"/>
+      <c r="AE13" s="206"/>
       <c r="AF13" s="128"/>
       <c r="AG13" s="119"/>
       <c r="AH13" s="114"/>
@@ -7530,7 +7528,7 @@
     </row>
     <row r="14" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="127"/>
-      <c r="C14" s="203"/>
+      <c r="C14" s="206"/>
       <c r="D14" s="122" t="str">
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M77",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Sverige</v>
@@ -7561,7 +7559,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M78",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Norge</v>
       </c>
-      <c r="AE14" s="203"/>
+      <c r="AE14" s="206"/>
       <c r="AF14" s="128"/>
       <c r="AG14" s="119"/>
       <c r="AH14" s="114"/>
@@ -7575,7 +7573,7 @@
       <c r="F15" s="114"/>
       <c r="G15" s="114"/>
       <c r="H15" s="114"/>
-      <c r="I15" s="203" t="s">
+      <c r="I15" s="206" t="s">
         <v>273</v>
       </c>
       <c r="J15" s="115" t="s">
@@ -7594,7 +7592,7 @@
       <c r="X15" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="Y15" s="203" t="s">
+      <c r="Y15" s="206" t="s">
         <v>275</v>
       </c>
       <c r="AA15" s="114"/>
@@ -7615,7 +7613,7 @@
       <c r="F16" s="114"/>
       <c r="G16" s="114"/>
       <c r="H16" s="114"/>
-      <c r="I16" s="203"/>
+      <c r="I16" s="206"/>
       <c r="J16" s="114"/>
       <c r="K16" s="114"/>
       <c r="L16" s="114"/>
@@ -7630,7 +7628,7 @@
       <c r="V16" s="114"/>
       <c r="W16" s="114"/>
       <c r="X16" s="114"/>
-      <c r="Y16" s="203"/>
+      <c r="Y16" s="206"/>
       <c r="AA16" s="114"/>
       <c r="AB16" s="114"/>
       <c r="AC16" s="114"/>
@@ -7649,7 +7647,7 @@
       <c r="F17" s="114"/>
       <c r="G17" s="114"/>
       <c r="H17" s="114"/>
-      <c r="I17" s="203"/>
+      <c r="I17" s="206"/>
       <c r="J17" s="115" t="s">
         <v>24</v>
       </c>
@@ -7668,7 +7666,7 @@
       <c r="X17" s="115" t="s">
         <v>120</v>
       </c>
-      <c r="Y17" s="203"/>
+      <c r="Y17" s="206"/>
       <c r="AA17" s="114"/>
       <c r="AB17" s="114"/>
       <c r="AC17" s="114"/>
@@ -7681,7 +7679,7 @@
     </row>
     <row r="18" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="127"/>
-      <c r="C18" s="203" t="s">
+      <c r="C18" s="206" t="s">
         <v>249</v>
       </c>
       <c r="D18" s="115" t="str">
@@ -7719,7 +7717,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M79",_Listor!$BX$3:$BX$18,0),1)</f>
         <v>Sydkorea</v>
       </c>
-      <c r="AE18" s="203" t="s">
+      <c r="AE18" s="206" t="s">
         <v>255</v>
       </c>
       <c r="AF18" s="128"/>
@@ -7729,7 +7727,7 @@
     </row>
     <row r="19" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="127"/>
-      <c r="C19" s="203"/>
+      <c r="C19" s="206"/>
       <c r="D19" s="114"/>
       <c r="E19" s="114"/>
       <c r="F19" s="114"/>
@@ -7758,7 +7756,7 @@
       <c r="AA19" s="114"/>
       <c r="AB19" s="114"/>
       <c r="AC19" s="114"/>
-      <c r="AE19" s="203"/>
+      <c r="AE19" s="206"/>
       <c r="AF19" s="128"/>
       <c r="AG19" s="119"/>
       <c r="AH19" s="114"/>
@@ -7766,7 +7764,7 @@
     </row>
     <row r="20" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="127"/>
-      <c r="C20" s="203"/>
+      <c r="C20" s="206"/>
       <c r="D20" s="115" t="str">
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M73",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Bosnien och Hercegovina</v>
@@ -7798,7 +7796,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M79",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Marocko</v>
       </c>
-      <c r="AE20" s="203"/>
+      <c r="AE20" s="206"/>
       <c r="AF20" s="128"/>
       <c r="AG20" s="119"/>
       <c r="AH20" s="114"/>
@@ -7807,7 +7805,7 @@
     <row r="21" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="127"/>
       <c r="E21" s="114"/>
-      <c r="F21" s="203" t="s">
+      <c r="F21" s="206" t="s">
         <v>266</v>
       </c>
       <c r="G21" s="115" t="s">
@@ -7838,7 +7836,7 @@
       <c r="AA21" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="AB21" s="203" t="s">
+      <c r="AB21" s="206" t="s">
         <v>268</v>
       </c>
       <c r="AD21" s="114"/>
@@ -7851,7 +7849,7 @@
     <row r="22" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="127"/>
       <c r="E22" s="114"/>
-      <c r="F22" s="203"/>
+      <c r="F22" s="206"/>
       <c r="G22" s="114"/>
       <c r="H22" s="114"/>
       <c r="I22" s="114"/>
@@ -7873,7 +7871,7 @@
       <c r="Y22" s="114"/>
       <c r="Z22" s="114"/>
       <c r="AA22" s="114"/>
-      <c r="AB22" s="203"/>
+      <c r="AB22" s="206"/>
       <c r="AD22" s="114"/>
       <c r="AE22" s="114"/>
       <c r="AF22" s="130"/>
@@ -7884,7 +7882,7 @@
     <row r="23" spans="2:35" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="127"/>
       <c r="E23" s="114"/>
-      <c r="F23" s="203"/>
+      <c r="F23" s="206"/>
       <c r="G23" s="115" t="s">
         <v>71</v>
       </c>
@@ -7896,11 +7894,11 @@
       <c r="M23" s="114"/>
       <c r="N23" s="114"/>
       <c r="O23" s="114"/>
-      <c r="P23" s="210" t="s">
+      <c r="P23" s="205" t="s">
         <v>318</v>
       </c>
-      <c r="Q23" s="210"/>
-      <c r="R23" s="210"/>
+      <c r="Q23" s="205"/>
+      <c r="R23" s="205"/>
       <c r="S23" s="114"/>
       <c r="T23" s="114"/>
       <c r="U23" s="114"/>
@@ -7912,7 +7910,7 @@
       <c r="AA23" s="115" t="s">
         <v>120</v>
       </c>
-      <c r="AB23" s="203"/>
+      <c r="AB23" s="206"/>
       <c r="AD23" s="114"/>
       <c r="AE23" s="114"/>
       <c r="AF23" s="128"/>
@@ -7921,7 +7919,7 @@
     </row>
     <row r="24" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="127"/>
-      <c r="C24" s="203" t="s">
+      <c r="C24" s="206" t="s">
         <v>250</v>
       </c>
       <c r="D24" s="115" t="str">
@@ -7954,7 +7952,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M80",_Listor!$BX$3:$BX$18,0),1)</f>
         <v>England</v>
       </c>
-      <c r="AE24" s="203" t="s">
+      <c r="AE24" s="206" t="s">
         <v>256</v>
       </c>
       <c r="AF24" s="128"/>
@@ -7964,7 +7962,7 @@
     </row>
     <row r="25" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="127"/>
-      <c r="C25" s="203"/>
+      <c r="C25" s="206"/>
       <c r="D25" s="114"/>
       <c r="E25" s="114"/>
       <c r="F25" s="114"/>
@@ -7989,7 +7987,7 @@
       <c r="AA25" s="114"/>
       <c r="AB25" s="114"/>
       <c r="AC25" s="114"/>
-      <c r="AE25" s="203"/>
+      <c r="AE25" s="206"/>
       <c r="AF25" s="128"/>
       <c r="AG25" s="119"/>
       <c r="AH25" s="114"/>
@@ -7997,7 +7995,7 @@
     </row>
     <row r="26" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="127"/>
-      <c r="C26" s="203"/>
+      <c r="C26" s="206"/>
       <c r="D26" s="115" t="str">
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M75",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Skottland</v>
@@ -8009,23 +8007,23 @@
       <c r="I26" s="114"/>
       <c r="J26" s="114"/>
       <c r="K26" s="114"/>
-      <c r="L26" s="210" t="s">
+      <c r="L26" s="205" t="s">
         <v>916</v>
       </c>
-      <c r="M26" s="210"/>
-      <c r="N26" s="210"/>
+      <c r="M26" s="205"/>
+      <c r="N26" s="205"/>
       <c r="O26" s="114"/>
-      <c r="P26" s="211" t="s">
+      <c r="P26" s="214" t="s">
         <v>922</v>
       </c>
-      <c r="Q26" s="212"/>
-      <c r="R26" s="213"/>
+      <c r="Q26" s="215"/>
+      <c r="R26" s="216"/>
       <c r="S26" s="114"/>
-      <c r="T26" s="210" t="s">
+      <c r="T26" s="205" t="s">
         <v>916</v>
       </c>
-      <c r="U26" s="210"/>
-      <c r="V26" s="210"/>
+      <c r="U26" s="205"/>
+      <c r="V26" s="205"/>
       <c r="W26" s="114"/>
       <c r="Z26" s="114"/>
       <c r="AA26" s="114"/>
@@ -8035,7 +8033,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M80",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>DR Kongo</v>
       </c>
-      <c r="AE26" s="203"/>
+      <c r="AE26" s="206"/>
       <c r="AF26" s="128"/>
       <c r="AG26" s="119"/>
       <c r="AH26" s="114"/>
@@ -8084,7 +8082,7 @@
       <c r="I28" s="114"/>
       <c r="J28" s="114"/>
       <c r="K28" s="114"/>
-      <c r="L28" s="203" t="s">
+      <c r="L28" s="206" t="s">
         <v>277</v>
       </c>
       <c r="M28" s="115" t="s">
@@ -8100,7 +8098,7 @@
       <c r="U28" s="115" t="s">
         <v>120</v>
       </c>
-      <c r="V28" s="203" t="s">
+      <c r="V28" s="206" t="s">
         <v>278</v>
       </c>
       <c r="X28" s="114"/>
@@ -8125,7 +8123,7 @@
       <c r="I29" s="114"/>
       <c r="J29" s="114"/>
       <c r="K29" s="114"/>
-      <c r="L29" s="203"/>
+      <c r="L29" s="206"/>
       <c r="M29" s="114"/>
       <c r="N29" s="114"/>
       <c r="O29" s="114"/>
@@ -8135,7 +8133,7 @@
       <c r="S29" s="114"/>
       <c r="T29" s="114"/>
       <c r="U29" s="114"/>
-      <c r="V29" s="203"/>
+      <c r="V29" s="206"/>
       <c r="Z29" s="114"/>
       <c r="AA29" s="114"/>
       <c r="AB29" s="114"/>
@@ -8156,7 +8154,7 @@
       <c r="I30" s="114"/>
       <c r="J30" s="114"/>
       <c r="K30" s="114"/>
-      <c r="L30" s="203"/>
+      <c r="L30" s="206"/>
       <c r="M30" s="115" t="s">
         <v>91</v>
       </c>
@@ -8170,7 +8168,7 @@
       <c r="U30" s="115" t="s">
         <v>114</v>
       </c>
-      <c r="V30" s="203"/>
+      <c r="V30" s="206"/>
       <c r="X30" s="114"/>
       <c r="Y30" s="114"/>
       <c r="Z30" s="114"/>
@@ -8222,7 +8220,7 @@
     </row>
     <row r="32" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="127"/>
-      <c r="C32" s="203" t="s">
+      <c r="C32" s="206" t="s">
         <v>257</v>
       </c>
       <c r="D32" s="115" t="str">
@@ -8255,7 +8253,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M86",_Listor!$BX$3:$BX$18,0),1)</f>
         <v>Österrike</v>
       </c>
-      <c r="AE32" s="203" t="s">
+      <c r="AE32" s="206" t="s">
         <v>261</v>
       </c>
       <c r="AF32" s="128"/>
@@ -8265,7 +8263,7 @@
     </row>
     <row r="33" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="127"/>
-      <c r="C33" s="203"/>
+      <c r="C33" s="206"/>
       <c r="D33" s="114"/>
       <c r="E33" s="114"/>
       <c r="F33" s="114"/>
@@ -8289,7 +8287,7 @@
       <c r="AA33" s="114"/>
       <c r="AB33" s="114"/>
       <c r="AC33" s="114"/>
-      <c r="AE33" s="203"/>
+      <c r="AE33" s="206"/>
       <c r="AF33" s="128"/>
       <c r="AG33" s="119"/>
       <c r="AH33" s="114"/>
@@ -8297,7 +8295,7 @@
     </row>
     <row r="34" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="127"/>
-      <c r="C34" s="203"/>
+      <c r="C34" s="206"/>
       <c r="D34" s="115" t="str">
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M83",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Kroatien</v>
@@ -8312,11 +8310,11 @@
       <c r="M34" s="114"/>
       <c r="N34" s="114"/>
       <c r="O34" s="114"/>
-      <c r="P34" s="210" t="s">
+      <c r="P34" s="205" t="s">
         <v>917</v>
       </c>
-      <c r="Q34" s="210"/>
-      <c r="R34" s="210"/>
+      <c r="Q34" s="205"/>
+      <c r="R34" s="205"/>
       <c r="S34" s="114"/>
       <c r="T34" s="114"/>
       <c r="U34" s="114"/>
@@ -8332,7 +8330,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M86",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Uruguay</v>
       </c>
-      <c r="AE34" s="203"/>
+      <c r="AE34" s="206"/>
       <c r="AF34" s="128"/>
       <c r="AG34" s="119"/>
       <c r="AH34" s="114"/>
@@ -8343,7 +8341,7 @@
       <c r="C35" s="114"/>
       <c r="D35" s="114"/>
       <c r="E35" s="114"/>
-      <c r="F35" s="203" t="s">
+      <c r="F35" s="206" t="s">
         <v>269</v>
       </c>
       <c r="G35" s="115" t="s">
@@ -8371,7 +8369,7 @@
       <c r="AA35" s="115" t="s">
         <v>93</v>
       </c>
-      <c r="AB35" s="203" t="s">
+      <c r="AB35" s="206" t="s">
         <v>271</v>
       </c>
       <c r="AD35" s="114"/>
@@ -8386,7 +8384,7 @@
       <c r="C36" s="114"/>
       <c r="D36" s="114"/>
       <c r="E36" s="114"/>
-      <c r="F36" s="203"/>
+      <c r="F36" s="206"/>
       <c r="G36" s="114"/>
       <c r="H36" s="114"/>
       <c r="I36" s="114"/>
@@ -8411,7 +8409,7 @@
       <c r="Y36" s="114"/>
       <c r="Z36" s="114"/>
       <c r="AA36" s="114"/>
-      <c r="AB36" s="203"/>
+      <c r="AB36" s="206"/>
       <c r="AD36" s="114"/>
       <c r="AE36" s="114"/>
       <c r="AF36" s="130"/>
@@ -8422,7 +8420,7 @@
     <row r="37" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="127"/>
       <c r="E37" s="114"/>
-      <c r="F37" s="203"/>
+      <c r="F37" s="206"/>
       <c r="G37" s="115" t="s">
         <v>91</v>
       </c>
@@ -8434,7 +8432,7 @@
       <c r="AA37" s="115" t="s">
         <v>83</v>
       </c>
-      <c r="AB37" s="203"/>
+      <c r="AB37" s="206"/>
       <c r="AE37" s="114"/>
       <c r="AF37" s="128"/>
       <c r="AH37" s="114"/>
@@ -8442,7 +8440,7 @@
     </row>
     <row r="38" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="127"/>
-      <c r="C38" s="203" t="s">
+      <c r="C38" s="206" t="s">
         <v>258</v>
       </c>
       <c r="D38" s="115" t="str">
@@ -8480,7 +8478,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M88",_Listor!$BX$3:$BX$18,0),1)</f>
         <v>Paraguay</v>
       </c>
-      <c r="AE38" s="203" t="s">
+      <c r="AE38" s="206" t="s">
         <v>262</v>
       </c>
       <c r="AF38" s="128"/>
@@ -8490,7 +8488,7 @@
     </row>
     <row r="39" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="127"/>
-      <c r="C39" s="203"/>
+      <c r="C39" s="206"/>
       <c r="D39" s="114"/>
       <c r="E39" s="114"/>
       <c r="F39" s="114"/>
@@ -8516,7 +8514,7 @@
       <c r="AA39" s="114"/>
       <c r="AB39" s="114"/>
       <c r="AC39" s="114"/>
-      <c r="AE39" s="203"/>
+      <c r="AE39" s="206"/>
       <c r="AF39" s="128"/>
       <c r="AG39" s="119"/>
       <c r="AH39" s="114"/>
@@ -8524,7 +8522,7 @@
     </row>
     <row r="40" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="127"/>
-      <c r="C40" s="203"/>
+      <c r="C40" s="206"/>
       <c r="D40" s="115" t="str">
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M84",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Argentina</v>
@@ -8552,7 +8550,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M88",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Iran</v>
       </c>
-      <c r="AE40" s="203"/>
+      <c r="AE40" s="206"/>
       <c r="AF40" s="128"/>
       <c r="AG40" s="119"/>
       <c r="AH40" s="114"/>
@@ -8566,7 +8564,7 @@
       <c r="F41" s="114"/>
       <c r="G41" s="114"/>
       <c r="H41" s="114"/>
-      <c r="I41" s="203" t="s">
+      <c r="I41" s="206" t="s">
         <v>274</v>
       </c>
       <c r="J41" s="115" t="s">
@@ -8585,7 +8583,7 @@
       <c r="X41" s="115" t="s">
         <v>93</v>
       </c>
-      <c r="Y41" s="203" t="s">
+      <c r="Y41" s="206" t="s">
         <v>276</v>
       </c>
       <c r="AA41" s="114"/>
@@ -8606,7 +8604,7 @@
       <c r="F42" s="114"/>
       <c r="G42" s="114"/>
       <c r="H42" s="114"/>
-      <c r="I42" s="203"/>
+      <c r="I42" s="206"/>
       <c r="J42" s="114"/>
       <c r="K42" s="114"/>
       <c r="L42" s="114"/>
@@ -8622,7 +8620,7 @@
       <c r="V42" s="114"/>
       <c r="W42" s="114"/>
       <c r="X42" s="114"/>
-      <c r="Y42" s="203"/>
+      <c r="Y42" s="206"/>
       <c r="AA42" s="114"/>
       <c r="AB42" s="114"/>
       <c r="AC42" s="114"/>
@@ -8640,7 +8638,7 @@
       <c r="F43" s="114"/>
       <c r="G43" s="114"/>
       <c r="H43" s="114"/>
-      <c r="I43" s="203"/>
+      <c r="I43" s="206"/>
       <c r="J43" s="115" t="s">
         <v>79</v>
       </c>
@@ -8660,7 +8658,7 @@
       <c r="X43" s="115" t="s">
         <v>114</v>
       </c>
-      <c r="Y43" s="203"/>
+      <c r="Y43" s="206"/>
       <c r="AA43" s="114"/>
       <c r="AB43" s="114"/>
       <c r="AC43" s="114"/>
@@ -8672,7 +8670,7 @@
     </row>
     <row r="44" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="127"/>
-      <c r="C44" s="203" t="s">
+      <c r="C44" s="206" t="s">
         <v>259</v>
       </c>
       <c r="D44" s="115" t="str">
@@ -8708,7 +8706,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M85",_Listor!$BX$3:$BX$18,0),1)</f>
         <v>Schweiz</v>
       </c>
-      <c r="AE44" s="203" t="s">
+      <c r="AE44" s="206" t="s">
         <v>263</v>
       </c>
       <c r="AF44" s="128"/>
@@ -8718,7 +8716,7 @@
     </row>
     <row r="45" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="127"/>
-      <c r="C45" s="203"/>
+      <c r="C45" s="206"/>
       <c r="D45" s="114"/>
       <c r="E45" s="114"/>
       <c r="G45" s="114"/>
@@ -8744,7 +8742,7 @@
       <c r="AA45" s="114"/>
       <c r="AB45" s="114"/>
       <c r="AC45" s="114"/>
-      <c r="AE45" s="203"/>
+      <c r="AE45" s="206"/>
       <c r="AF45" s="128"/>
       <c r="AG45" s="119"/>
       <c r="AH45" s="114"/>
@@ -8752,7 +8750,7 @@
     </row>
     <row r="46" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="127"/>
-      <c r="C46" s="203"/>
+      <c r="C46" s="206"/>
       <c r="D46" s="122" t="str">
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M81",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Qatar</v>
@@ -8786,7 +8784,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M85",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Ecuador</v>
       </c>
-      <c r="AE46" s="203"/>
+      <c r="AE46" s="206"/>
       <c r="AF46" s="128"/>
       <c r="AG46" s="119"/>
       <c r="AH46" s="114"/>
@@ -8796,7 +8794,7 @@
       <c r="B47" s="127"/>
       <c r="D47" s="114"/>
       <c r="E47" s="114"/>
-      <c r="F47" s="203" t="s">
+      <c r="F47" s="206" t="s">
         <v>270</v>
       </c>
       <c r="G47" s="115" t="s">
@@ -8824,7 +8822,7 @@
       <c r="AA47" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="AB47" s="203" t="s">
+      <c r="AB47" s="206" t="s">
         <v>272</v>
       </c>
       <c r="AD47" s="114"/>
@@ -8836,7 +8834,7 @@
       <c r="B48" s="127"/>
       <c r="D48" s="114"/>
       <c r="E48" s="114"/>
-      <c r="F48" s="203"/>
+      <c r="F48" s="206"/>
       <c r="G48" s="114"/>
       <c r="H48" s="114"/>
       <c r="I48" s="114"/>
@@ -8858,7 +8856,7 @@
       <c r="Y48" s="114"/>
       <c r="Z48" s="114"/>
       <c r="AA48" s="114"/>
-      <c r="AB48" s="203"/>
+      <c r="AB48" s="206"/>
       <c r="AD48" s="114"/>
       <c r="AF48" s="130"/>
       <c r="AG48" s="114"/>
@@ -8870,7 +8868,7 @@
       <c r="C49" s="114"/>
       <c r="D49" s="114"/>
       <c r="E49" s="114"/>
-      <c r="F49" s="203"/>
+      <c r="F49" s="206"/>
       <c r="G49" s="115" t="s">
         <v>79</v>
       </c>
@@ -8896,7 +8894,7 @@
       <c r="AA49" s="115" t="s">
         <v>114</v>
       </c>
-      <c r="AB49" s="203"/>
+      <c r="AB49" s="206"/>
       <c r="AD49" s="114"/>
       <c r="AF49" s="130"/>
       <c r="AG49" s="114"/>
@@ -8905,7 +8903,7 @@
     </row>
     <row r="50" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="127"/>
-      <c r="C50" s="203" t="s">
+      <c r="C50" s="206" t="s">
         <v>260</v>
       </c>
       <c r="D50" s="115" t="str">
@@ -8941,7 +8939,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M87",_Listor!$BX$3:$BX$18,0),1)</f>
         <v>Portugal</v>
       </c>
-      <c r="AE50" s="203" t="s">
+      <c r="AE50" s="206" t="s">
         <v>264</v>
       </c>
       <c r="AF50" s="128"/>
@@ -8951,7 +8949,7 @@
     </row>
     <row r="51" spans="2:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="127"/>
-      <c r="C51" s="203"/>
+      <c r="C51" s="206"/>
       <c r="D51" s="114"/>
       <c r="E51" s="114"/>
       <c r="F51" s="114"/>
@@ -8978,7 +8976,7 @@
       <c r="AA51" s="114"/>
       <c r="AB51" s="114"/>
       <c r="AC51" s="114"/>
-      <c r="AE51" s="203"/>
+      <c r="AE51" s="206"/>
       <c r="AF51" s="128"/>
       <c r="AG51" s="119"/>
       <c r="AH51" s="114"/>
@@ -8986,7 +8984,7 @@
     </row>
     <row r="52" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="127"/>
-      <c r="C52" s="203"/>
+      <c r="C52" s="206"/>
       <c r="D52" s="122" t="str">
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M82",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Mexiko</v>
@@ -9020,7 +9018,7 @@
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M87",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Senegal</v>
       </c>
-      <c r="AE52" s="203"/>
+      <c r="AE52" s="206"/>
       <c r="AF52" s="128"/>
       <c r="AG52" s="119"/>
       <c r="AH52" s="114"/>
@@ -9064,15 +9062,21 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="P34:R34"/>
+    <mergeCell ref="T26:V26"/>
+    <mergeCell ref="L28:L30"/>
+    <mergeCell ref="I41:I43"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="W13:Y13"/>
+    <mergeCell ref="Y41:Y43"/>
+    <mergeCell ref="Y15:Y17"/>
+    <mergeCell ref="V28:V30"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C24:C26"/>
     <mergeCell ref="F35:F37"/>
     <mergeCell ref="AE50:AE52"/>
     <mergeCell ref="AE44:AE46"/>
@@ -9085,26 +9089,20 @@
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="AB35:AB37"/>
     <mergeCell ref="AB47:AB49"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C24:C26"/>
     <mergeCell ref="F47:F49"/>
     <mergeCell ref="AE32:AE34"/>
     <mergeCell ref="AE24:AE26"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="C18:C20"/>
     <mergeCell ref="O3:S4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="W13:Y13"/>
-    <mergeCell ref="Y41:Y43"/>
-    <mergeCell ref="Y15:Y17"/>
-    <mergeCell ref="V28:V30"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="P34:R34"/>
-    <mergeCell ref="T26:V26"/>
-    <mergeCell ref="L28:L30"/>
-    <mergeCell ref="I41:I43"/>
-    <mergeCell ref="I15:I17"/>
     <mergeCell ref="F21:F23"/>
   </mergeCells>
   <conditionalFormatting sqref="P26:R26">
@@ -9233,24 +9231,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="111" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="196" t="s">
         <v>925</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="194"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="192"/>
     </row>
     <row r="2" spans="1:50" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="202" t="s">
+      <c r="A2" s="204" t="s">
         <v>924</v>
       </c>
-      <c r="B2" s="202"/>
-      <c r="C2" s="202"/>
-      <c r="D2" s="202"/>
-      <c r="E2" s="202"/>
-      <c r="F2" s="202"/>
+      <c r="B2" s="204"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
       <c r="K2" s="111"/>
       <c r="L2" s="111"/>
       <c r="M2" s="111"/>
@@ -9780,12 +9778,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="215" t="s">
+      <c r="A1" s="217" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="194"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="192"/>
       <c r="F1" s="34" t="s">
         <v>14</v>
       </c>
@@ -10497,17 +10495,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="216" t="s">
+      <c r="A1" s="218" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
     </row>
     <row r="2" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
@@ -30198,17 +30196,17 @@
       <c r="BO1" t="s">
         <v>292</v>
       </c>
-      <c r="BT1" s="218" t="s">
+      <c r="BT1" s="220" t="s">
         <v>316</v>
       </c>
-      <c r="BU1" s="217"/>
-      <c r="BV1" s="217"/>
-      <c r="BX1" s="219" t="s">
+      <c r="BU1" s="219"/>
+      <c r="BV1" s="219"/>
+      <c r="BX1" s="221" t="s">
         <v>317</v>
       </c>
-      <c r="BY1" s="217"/>
-      <c r="BZ1" s="217"/>
-      <c r="CA1" s="217"/>
+      <c r="BY1" s="219"/>
+      <c r="BZ1" s="219"/>
+      <c r="CA1" s="219"/>
     </row>
     <row r="2" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -32534,12 +32532,12 @@
       <c r="BV21" s="139" t="s">
         <v>340</v>
       </c>
-      <c r="BX21" s="218" t="s">
+      <c r="BX21" s="220" t="s">
         <v>341</v>
       </c>
-      <c r="BY21" s="217"/>
-      <c r="BZ21" s="217"/>
-      <c r="CA21" s="217"/>
+      <c r="BY21" s="219"/>
+      <c r="BZ21" s="219"/>
+      <c r="CA21" s="219"/>
     </row>
     <row r="22" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
